--- a/tools/sample.xlsx
+++ b/tools/sample.xlsx
@@ -437,7 +437,7 @@
         <v>me@qq.com</v>
       </c>
       <c r="E2" t="str">
-        <v>2026-08-20 22:36</v>
+        <v>2026-08-20 23:11</v>
       </c>
     </row>
     <row r="3">
@@ -454,7 +454,7 @@
         <v/>
       </c>
       <c r="E3" t="str">
-        <v>2026-08-20 22:36</v>
+        <v>2026-08-20 23:11</v>
       </c>
     </row>
   </sheetData>
